--- a/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
+++ b/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -433,17 +433,17 @@
     <col width="61" customWidth="1" min="15" max="15"/>
     <col width="170" customWidth="1" min="16" max="16"/>
     <col width="52" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
@@ -3910,6 +3910,668 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>var x int = 42</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>func logMessage(msg string) {
+    fmt.Println(msg)
+}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>func add(a int, b int) int {
+    return a + b
+}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>if x &gt; 0 {
+    return 1
+} else {
+    return 0
+}</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>for x &gt; 0 {
+    x = x - 1
+}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>if err := do_something(); err != nil {
+    handle(err)
+}</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>panic("Error")</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>go do_work()</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ch &lt;- 42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>msg := &lt;-ch
+handle(msg)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>// comment</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/* line 1
+   line 2 */</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>fmt.Println("Hello, World!")</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>import "fmt"</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>switch x {
+case 1:
+    return 1
+case 2:
+    return 2
+default:
+    return 0
+}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>const MAX = 100</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>a + b</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>a - b</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>a * b</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>a / b</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>a % b</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>math.Floor(a)</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>math.Round(a)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>a++</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>a--</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>a &lt;&lt; b</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>a &gt;&gt; b</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>a &amp; b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Haskell</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>let x = 42</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>logMessage :: String -&gt; IO ()
+logMessage msg = putStrLn msg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>add :: Int -&gt; Int -&gt; Int
+add a b = a + b</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>if x &gt; 0 then 1 else 0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>loop x = if x &gt; 0 then loop (x - 1) else return ()</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>do_something `catch` \(e :: SomeException) -&gt; handle e</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>error "Error"</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>forkIO (do_work)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>writeChan chan 42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>msg &lt;- readChan chan
+handle msg</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-- comment</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{- line 1
+   line 2 -}</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>putStrLn "Hello, World!"</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>import Data.List</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>case x of
+    1 -&gt; 1
+    2 -&gt; 2
+    _ -&gt; 0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>maxVal = 100</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>a + b</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>a - b</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>a * b</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>a / b</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>a `mod` b</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>floor a</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>round a</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>a + 1</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>a - 1</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>shiftL a b</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>shiftR a b</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>a .&amp;. b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>let x: number = 42;</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>function logMessage(msg: string): void {
+    console.log(msg);
+}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>function add(a: number, b: number): number {
+    return a + b;
+}</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>if (x &gt; 0) {
+    return 1;
+} else {
+    return 0;
+}</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>while (x &gt; 0) {
+    x = x - 1;
+}</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>try {
+    do_something();
+} catch (e) {
+    handle(e);
+}</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>throw new Error("Error");</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>new Worker('worker.js');</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>worker.postMessage(42);</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>worker.onmessage = (e) =&gt; { handle(e.data); };</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>// comment</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/* line 1
+   line 2 */</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>console.log("Hello, World!");</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>import { add } from './math';</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>switch (x) {
+    case 1:
+        return 1;
+    case 2:
+        return 2;
+    default:
+        return 0;
+}</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>const MAX: number = 100;</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>a + b</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>a - b</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>a * b</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>a / b</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>a % b</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Math.floor(a)</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Math.round(a)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>a++</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>a--</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>a &lt;&lt; b</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>a &gt;&gt; b</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>a &amp; b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tcl</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>set x 42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>proc logMessage {msg} {
+    puts $msg
+}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>proc add {a b} {
+    return [expr {$a + $b}]
+}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>if {$x &gt; 0} {
+    return 1
+} else {
+    return 0
+}</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>while {$x &gt; 0} {
+    set x [expr {$x - 1}]
+}</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>try {
+    do_something
+} on error {e} {
+    handle $e
+}</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>error "Error"</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>thread::create { do_work }</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>thread::send $id $msg</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vwait msg; handle $msg</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t># comment</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>puts "Hello, World!"</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>package require Tcl</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>switch $x {
+    1 {
+        return 1
+    }
+    2 {
+        return 2
+    }
+    default {
+        return 0
+    }
+}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>set MAX 100</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>[expr {$a + $b}]</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>[expr {$a - $b}]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>[expr {$a * $b}]</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>[expr {$a / $b}]</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>[expr {$a % $b}]</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>[expr {floor($a)}]</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>[expr {round($a)}]</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>incr a</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>incr a -1</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>[expr {$a &lt;&lt; $b}]</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>[expr {$a &gt;&gt; $b}]</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>[expr {$a &amp; $b}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
+++ b/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="19" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="69" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,6 +592,11 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>Bitwise</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Float4VectorMultiplication</t>
         </is>
       </c>
     </row>
@@ -758,6 +764,11 @@
           <t>a &amp; b</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -927,6 +938,11 @@
           <t>a &amp; b</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1090,6 +1106,11 @@
       <c r="AC4" t="inlineStr">
         <is>
           <t>a &amp; b</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>for i in 0..4 { c[i] = a[i] * b[i]; }</t>
         </is>
       </c>
     </row>
@@ -1251,6 +1272,11 @@
           <t>a &amp; b</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>c = [ai * bi for ai, bi in zip(a, b)]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1418,6 +1444,11 @@
       <c r="AC6" t="inlineStr">
         <is>
           <t>a &amp; b</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>$c = array_map(fn($ai, $bi) =&gt; $ai * $bi, $a, $b);</t>
         </is>
       </c>
     </row>
@@ -1587,6 +1618,11 @@
           <t>((a &amp; b))</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>for i in {0..3}; do c[$i]=$(echo "${a[$i]} * ${b[$i]}" | bc); done</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1753,6 +1789,11 @@
           <t>a -band b</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>$c = 0..3 | ForEach-Object { $a[$_] * $b[$_] }</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1903,6 +1944,11 @@
       <c r="AC9" t="inlineStr">
         <is>
           <t>set /a res="a &amp; b"</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2080,6 +2126,11 @@
           <t>a &amp; b</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>SELECT a1*b1, a2*b2, a3*b3, a4*b4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2236,6 +2287,11 @@
           <t>A band B</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[Ai * Bi || {Ai, Bi} &lt;- lists:zip(A, B)].</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2386,6 +2442,11 @@
       <c r="AC12" t="inlineStr">
         <is>
           <t>(logand a b)</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>(mapcar #'* a b)</t>
         </is>
       </c>
     </row>
@@ -2552,6 +2613,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>for $i in 1 to 4 return $a[$i] * $b[$i]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2696,6 +2762,11 @@
         </is>
       </c>
       <c r="AC14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2863,6 +2934,11 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>a &amp; b</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>c.x = a.x * b.x; c.y = a.y * b.y; c.z = a.z * b.z; c.w = a.w * b.w;</t>
         </is>
       </c>
     </row>
@@ -3043,6 +3119,11 @@
           <t>and eax, ebx</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>mulps xmm0, xmm1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3215,6 +3296,12 @@
           <t>and t0, t1, t2</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>vsetvli t0, x0, e32, m1
+vfmul.vv v1, v2, v3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3389,6 +3476,11 @@
           <t>and x0, x1, x2</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>fmul v0.4s, v1.4s, v2.4s</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3539,6 +3631,11 @@
       <c r="AC19" t="inlineStr">
         <is>
           <t>Res is A /\ B</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>maplist(multiply, A, B, C).</t>
         </is>
       </c>
     </row>
@@ -3756,6 +3853,13 @@
           <t>iand</t>
         </is>
       </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>fload_1
+fload_2
+fmul</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3907,6 +4011,11 @@
       <c r="AC21" t="inlineStr">
         <is>
           <t>a land b</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Array.map2 (fun ai bi -&gt; ai *. bi) a b</t>
         </is>
       </c>
     </row>
@@ -4077,6 +4186,11 @@
           <t>a &amp; b</t>
         </is>
       </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>for i := range a { c[i] = a[i] * b[i] }</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4229,6 +4343,11 @@
       <c r="AC23" t="inlineStr">
         <is>
           <t>a .&amp;. b</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>zipWith (*) a b</t>
         </is>
       </c>
     </row>
@@ -4398,6 +4517,11 @@
       <c r="AC24" t="inlineStr">
         <is>
           <t>a &amp; b</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>const c = a.map((v, i) =&gt; v * b[i]);</t>
         </is>
       </c>
     </row>
@@ -4571,6 +4695,11 @@
           <t>[expr {$a &amp; $b}]</t>
         </is>
       </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>foreach ai $a bi $b { lappend c [expr {$ai * $bi}] }</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
+++ b/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AG25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,10 @@
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="19" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
-    <col width="69" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="69" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,10 +594,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Bitwise</t>
+          <t>BitAnd</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
+        <is>
+          <t>BitOr</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>BitXor</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>BitNot</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
         </is>
@@ -766,6 +784,21 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
         </is>
       </c>
@@ -940,6 +973,21 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
         </is>
       </c>
@@ -1109,6 +1157,21 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>!a</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>for i in 0..4 { c[i] = a[i] * b[i]; }</t>
         </is>
@@ -1274,6 +1337,21 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>c = [ai * bi for ai, bi in zip(a, b)]</t>
         </is>
       </c>
@@ -1447,6 +1525,21 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>$c = array_map(fn($ai, $bi) =&gt; $ai * $bi, $a, $b);</t>
         </is>
@@ -1620,6 +1713,21 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
+          <t>((a | b))</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>((a ^ b))</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>((~a))</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>for i in {0..3}; do c[$i]=$(echo "${a[$i]} * ${b[$i]}" | bc); done</t>
         </is>
       </c>
@@ -1791,6 +1899,21 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>a -bor b</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>a -bxor b</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>-bnot a</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>$c = 0..3 | ForEach-Object { $a[$_] * $b[$_] }</t>
         </is>
       </c>
@@ -1947,6 +2070,21 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>set /a res="a | b"</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>set /a res="a ^ b"</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>set /a res="~a"</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2128,6 +2266,21 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>SELECT a1*b1, a2*b2, a3*b3, a4*b4</t>
         </is>
       </c>
@@ -2289,6 +2442,21 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>A bor B</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>A bxor B</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>bnot A</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>[Ai * Bi || {Ai, Bi} &lt;- lists:zip(A, B)].</t>
         </is>
       </c>
@@ -2445,6 +2613,21 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>(logior a b)</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>(logxor a b)</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>(lognot a)</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>(mapcar #'* a b)</t>
         </is>
@@ -2615,6 +2798,21 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>for $i in 1 to 4 return $a[$i] * $b[$i]</t>
         </is>
       </c>
@@ -2767,6 +2965,21 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2937,6 +3150,21 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>c.x = a.x * b.x; c.y = a.y * b.y; c.z = a.z * b.z; c.w = a.w * b.w;</t>
         </is>
@@ -3121,6 +3349,21 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
+          <t>or eax, ebx</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>xor eax, ebx</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>not eax</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
           <t>mulps xmm0, xmm1</t>
         </is>
       </c>
@@ -3298,6 +3541,21 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
+          <t>or t0, t1, t2</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>xor t0, t1, t2</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>not t0, t1</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
           <t>vsetvli t0, x0, e32, m1
 vfmul.vv v1, v2, v3</t>
         </is>
@@ -3478,6 +3736,21 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
+          <t>orr x0, x1, x2</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>eor x0, x1, x2</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>mvn x0, x1</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
           <t>fmul v0.4s, v1.4s, v2.4s</t>
         </is>
       </c>
@@ -3634,6 +3907,21 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>Res is A \/ B</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Res is A xor B</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Res is \ A</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>maplist(multiply, A, B, C).</t>
         </is>
@@ -3855,6 +4143,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
+          <t>ior</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>ixor</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>iconst_m1
+ixor</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>fload_1
 fload_2
 fmul</t>
@@ -4014,6 +4318,21 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr">
+        <is>
+          <t>a lor b</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>a lxor b</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>lnot a</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Array.map2 (fun ai bi -&gt; ai *. bi) a b</t>
         </is>
@@ -4188,6 +4507,21 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>^a</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>for i := range a { c[i] = a[i] * b[i] }</t>
         </is>
       </c>
@@ -4346,6 +4680,21 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
+        <is>
+          <t>a .|. b</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>xor a b</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>complement a</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>zipWith (*) a b</t>
         </is>
@@ -4520,6 +4869,21 @@
         </is>
       </c>
       <c r="AD24" t="inlineStr">
+        <is>
+          <t>a | b</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>a ^ b</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>~a</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>const c = a.map((v, i) =&gt; v * b[i]);</t>
         </is>
@@ -4697,6 +5061,21 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
+          <t>[expr {$a | $b}]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[expr {$a ^ $b}]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[expr {~$a}]</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
           <t>foreach ai $a bi $b { lappend c [expr {$ai * $bi}] }</t>
         </is>
       </c>

--- a/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
+++ b/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG25"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="20" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
     <col width="69" customWidth="1" min="33" max="33"/>
+    <col width="87" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -615,6 +616,11 @@
       <c r="AG1" t="inlineStr">
         <is>
           <t>Float4VectorMultiplication</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Float4VectorDotProduct</t>
         </is>
       </c>
     </row>
@@ -802,6 +808,11 @@
           <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>float dot = 0; for (int i = 0; i &lt; 4; i++) dot += a[i] * b[i];</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -991,6 +1002,11 @@
           <t>for (int i = 0; i &lt; 4; i++) c[i] = a[i] * b[i];</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>float dot = 0; for (int i = 0; i &lt; 4; i++) dot += a[i] * b[i];</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1174,6 +1190,11 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>for i in 0..4 { c[i] = a[i] * b[i]; }</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>let dot: f32 = a.iter().zip(b.iter()).map(|(x, y)| x * y).sum();</t>
         </is>
       </c>
     </row>
@@ -1355,6 +1376,11 @@
           <t>c = [ai * bi for ai, bi in zip(a, b)]</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>dot = sum(ai * bi for ai, bi in zip(a, b))</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1542,6 +1568,11 @@
       <c r="AG6" t="inlineStr">
         <is>
           <t>$c = array_map(fn($ai, $bi) =&gt; $ai * $bi, $a, $b);</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>$dot = array_sum(array_map(fn($ai, $bi) =&gt; $ai * $bi, $a, $b));</t>
         </is>
       </c>
     </row>
@@ -1731,6 +1762,11 @@
           <t>for i in {0..3}; do c[$i]=$(echo "${a[$i]} * ${b[$i]}" | bc); done</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>dot=0; for i in {0..3}; do dot=$(echo "$dot + (${a[$i]} * ${b[$i]})" | bc); done</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1917,6 +1953,11 @@
           <t>$c = 0..3 | ForEach-Object { $a[$_] * $b[$_] }</t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>$dot = 0; 0..3 | ForEach-Object { $dot += $a[$_] * $b[$_] }</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2085,6 +2126,11 @@
         </is>
       </c>
       <c r="AG9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2284,6 +2330,11 @@
           <t>SELECT a1*b1, a2*b2, a3*b3, a4*b4</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>SELECT a1*b1 + a2*b2 + a3*b3 + a4*b4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2460,6 +2511,11 @@
           <t>[Ai * Bi || {Ai, Bi} &lt;- lists:zip(A, B)].</t>
         </is>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Dot = lists:foldl(fun({Ai, Bi}, Acc) -&gt; Ai * Bi + Acc end, 0.0, lists:zip(A, B)).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2630,6 +2686,11 @@
       <c r="AG12" t="inlineStr">
         <is>
           <t>(mapcar #'* a b)</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>(reduce #'+ (mapcar #'* a b))</t>
         </is>
       </c>
     </row>
@@ -2816,6 +2877,11 @@
           <t>for $i in 1 to 4 return $a[$i] * $b[$i]</t>
         </is>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>sum(for $i in 1 to 4 return $a[$i] * $b[$i])</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2980,6 +3046,11 @@
         </is>
       </c>
       <c r="AG14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3167,6 +3238,11 @@
       <c r="AG15" t="inlineStr">
         <is>
           <t>c.x = a.x * b.x; c.y = a.y * b.y; c.z = a.z * b.z; c.w = a.w * b.w;</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>float dot = a.x * b.x + a.y * b.y + a.z * b.z + a.w * b.w;</t>
         </is>
       </c>
     </row>
@@ -3367,6 +3443,11 @@
           <t>mulps xmm0, xmm1</t>
         </is>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>dpps xmm0, xmm1, 0xF1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3560,6 +3641,13 @@
 vfmul.vv v1, v2, v3</t>
         </is>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>vsetvli t0, x0, e32, m1
+vfmul.vv v1, v2, v3
+vfredusum.vs v4, v1, v5</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3754,6 +3842,13 @@
           <t>fmul v0.4s, v1.4s, v2.4s</t>
         </is>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>fmul v0.4s, v1.4s, v2.4s
+faddp v0.4s, v0.4s, v0.4s
+faddp s0, v0.2s</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3924,6 +4019,11 @@
       <c r="AG19" t="inlineStr">
         <is>
           <t>maplist(multiply, A, B, C).</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>dot_product(A, B, Dot) :- maplist(multiply, A, B, Products), sum_list(Products, Dot).</t>
         </is>
       </c>
     </row>
@@ -4164,6 +4264,14 @@
 fmul</t>
         </is>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>fload_1 ; a[i]
+fload_2 ; b[i]
+fmul
+fadd</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4335,6 +4443,11 @@
       <c r="AG21" t="inlineStr">
         <is>
           <t>Array.map2 (fun ai bi -&gt; ai *. bi) a b</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>let dot = List.fold_left2 (fun acc ai bi -&gt; acc +. ai *. bi) 0.0 a b</t>
         </is>
       </c>
     </row>
@@ -4525,6 +4638,12 @@
           <t>for i := range a { c[i] = a[i] * b[i] }</t>
         </is>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>dot := 0.0
+for i := range a { dot += a[i] * b[i] }</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4697,6 +4816,11 @@
       <c r="AG23" t="inlineStr">
         <is>
           <t>zipWith (*) a b</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>dot = sum $ zipWith (*) a b</t>
         </is>
       </c>
     </row>
@@ -4886,6 +5010,11 @@
       <c r="AG24" t="inlineStr">
         <is>
           <t>const c = a.map((v, i) =&gt; v * b[i]);</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>const dot = a.reduce((acc, v, i) =&gt; acc + v * b[i], 0);</t>
         </is>
       </c>
     </row>
@@ -5079,6 +5208,12 @@
           <t>foreach ai $a bi $b { lappend c [expr {$ai * $bi}] }</t>
         </is>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>set dot 0
+foreach ai $a bi $b { set dot [expr {$dot + ($ai * $bi)}] }</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
+++ b/_downloads/9191b3aaddb409bf44ab506fdd8ae8c6/programming_matrix.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -81817,6 +81817,6613 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>var</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>!=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>func</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>logMessage</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>String</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>print</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>func</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>add</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>-&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>if</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>else</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>switch</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>case</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>case</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>default</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>while</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>for</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>i</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>in</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>//</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve"> body</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>do</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>try</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>doSomething</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>catch</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>handle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>error</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>throw</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>MyError</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>error</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Thread</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>detachNewThread</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>doWork</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>await</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>actor</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>handle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>//</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve"> comment</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>/*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t xml:space="preserve"> line 1
+   line 2 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>*/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>print</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>Hello, World!</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>import</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="000e84b5"/>
+            </rPr>
+            <t>Foundation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>let</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>MAX</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>100</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>%</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>floor</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>round</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&lt;&lt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&amp;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>|</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>^</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>~</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>let</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>c</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>zip</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>map</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>let</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>dot</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>zip</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>map</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>reduce</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>let</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>c</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0.0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Kotlin</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>var</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>!</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>fun</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>logMessage</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>String</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>println</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>fun</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0006287e"/>
+            </rPr>
+            <t>add</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>Int</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>return</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>if</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>else</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>when</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>else</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>while</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>x</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>for</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>i</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>in</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>until</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>// body</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>try</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>doSomething</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>catch</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>e</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Exception</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>handle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>e</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>throw</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Exception</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>Error</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>thread</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>doWork</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>channel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>send</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>channel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>receive</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>handle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>msg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>// comment</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>/* line 1
+   line 2 */</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>println</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>Hello, World!</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>import</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="000e84b5"/>
+            </rPr>
+            <t>kotlin.math.*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>const</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>MAX</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>%</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>floor</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>round</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>shl</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>shr</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>and</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>xor</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>inv</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>c</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>zip</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>ai</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>bi</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>ai</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>bi</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>dot</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>zip</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>ai</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>bi</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>ai</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>bi</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>sum</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00bb60d5"/>
+            </rPr>
+            <t>c</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>floatArrayOf</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>a</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>b</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>0.0f</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
